--- a/9984.T_report.xlsx
+++ b/9984.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,58 +449,996 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="I2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2022-07-26</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1390.22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1344.22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-3.31</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1967</v>
+      </c>
+      <c r="I2" t="n">
+        <v>964941</v>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>総取引回数</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="3">
-      <c r="I3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2022-08-15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1443.82</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1367.67</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1879</v>
+      </c>
+      <c r="I3" t="n">
+        <v>912167</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>勝率</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2023-06-02</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1351.54</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1471.03</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="G4" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1905</v>
+      </c>
+      <c r="I4" t="n">
+        <v>990911</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>総利益率</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>97.08%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="I5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-01-12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2024-02-08</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1597.95</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1817</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2118</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1124629</v>
+      </c>
+      <c r="J5" t="n">
+        <v>27</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>平均保有日数</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0日</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5.6日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024-06-14</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2339.07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2502.91</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2328</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1201076</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1970823</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2357.32</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2259.2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-4.36</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2352</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1148731</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>970823</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-10-30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2375.49</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2226.9</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-6.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-6.45</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2226</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1074653</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>56367</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-12-13</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2322.22</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2242.06</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-3.45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-3.65</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2112</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1035444</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-05-29</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1976.41</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1896.73</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-4.03</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-4.23</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2029</v>
+      </c>
+      <c r="I10" t="n">
+        <v>991671</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2016.84</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2161.04</v>
+      </c>
+      <c r="F11" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2054</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1060515</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-07-28</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2926.67</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3128.83</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2194</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1131576</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-08-28</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3641.8</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3963.35</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="G13" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2363</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1229124</v>
+      </c>
+      <c r="J13" t="n">
+        <v>7</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-09-24</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4469.26</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4733.1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2531</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1299156</v>
+      </c>
+      <c r="J14" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4993.03</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5727.51</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="G15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2789</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1487476</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025-10-14</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5559.05</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5207.51</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2881</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1390531</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2025-10-15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2025-10-16</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5484.08</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5943.25</v>
+      </c>
+      <c r="F17" t="n">
+        <v>8.369999999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2897</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1504059</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-10-20</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5755.22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>6231.31</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3133</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1625344</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5922.66</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5635.24</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-4.85</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3172</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1543296</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6364.98</v>
+      </c>
+      <c r="E20" t="n">
+        <v>6812.41</v>
+      </c>
+      <c r="F20" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="G20" t="n">
+        <v>6.82</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3195</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1648587</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6572.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6274.95</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-4.53</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-4.72</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3223</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1570754</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7077.07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7833.16</v>
+      </c>
+      <c r="F22" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3309</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1735258</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>7498.49</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8532.459999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G23" t="n">
+        <v>13.58</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3710</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1970823</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>take_profit</t>
         </is>
       </c>
     </row>

--- a/9984.T_report.xlsx
+++ b/9984.T_report.xlsx
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1390.22</v>
+        <v>1390.23</v>
       </c>
       <c r="E2" t="n">
         <v>1344.22</v>
@@ -545,7 +545,7 @@
         <v>1443.82</v>
       </c>
       <c r="E3" t="n">
-        <v>1367.67</v>
+        <v>1367.66</v>
       </c>
       <c r="F3" t="n">
         <v>-5.27</v>
@@ -710,7 +710,7 @@
         <v>2328</v>
       </c>
       <c r="I6" t="n">
-        <v>1201076</v>
+        <v>1201075</v>
       </c>
       <c r="J6" t="n">
         <v>9</v>
@@ -1021,7 +1021,7 @@
         <v>2363</v>
       </c>
       <c r="I13" t="n">
-        <v>1229124</v>
+        <v>1229125</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>
